--- a/week3/manual_gold/301581_黄山谷捷_gold.xlsx
+++ b/week3/manual_gold/301581_黄山谷捷_gold.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,16 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>数据来源类型</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -502,6 +512,11 @@
           <t>2012年6月12日，谷捷有限由昆山谷捷出资1000万元设立，持股100%</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -544,6 +559,11 @@
           <t>2021年4月吸收合并昆山谷捷，谷捷有限注册资本由1000万元变更为1200万元，黄山供销集团以被合并方昆山谷捷账面净资产出资，增资156万元</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -586,6 +606,11 @@
           <t>张俊武增资22万元</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -628,6 +653,11 @@
           <t>周斌增资22万元</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -670,6 +700,11 @@
           <t>2021年11月，赛格高技术认缴462.8571万元注册资本，增资价格为22.42元/注册资本</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -712,6 +747,11 @@
           <t>上汽科技认缴51.4286万元注册资本，增资价格为22.42元/注册资本</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -754,6 +794,11 @@
           <t>2022年5月，新增注册资本90.2256万元由员工持股平台黄山佳捷全额认缴，增资价格为23.55元/注册资本</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -794,6 +839,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>2022年9月整体变更为股份公司，净资产20152.51万元按1:0.29773折为6000万股</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>直接披露</t>
         </is>
       </c>
     </row>
@@ -808,7 +858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -862,6 +912,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>时点说明</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -914,6 +969,11 @@
           <t>设立时昆山谷捷出资1000万元，持股100%</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>公司设立后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -966,6 +1026,11 @@
           <t>本次股权转让后黄山供销集团持股78%</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>本次股权转让完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1018,6 +1083,11 @@
           <t>张俊武持股11%</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>本次股权转让完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1070,6 +1140,11 @@
           <t>周斌持股11%</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>本次股权转让完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1122,6 +1197,7 @@
           <t>吸收合并后黄山供销集团出资936万元，持股78%</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1174,6 +1250,7 @@
           <t>张俊武出资132万元</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1226,6 +1303,7 @@
           <t>周斌出资132万元</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1278,6 +1356,11 @@
           <t>本次增资完成后，黄山供销集团持股54.60%</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>本次增资完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1330,6 +1413,11 @@
           <t>赛格高技术持股27.00%</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>本次增资完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1382,6 +1470,11 @@
           <t>张俊武持股7.70%</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>本次增资完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1434,6 +1527,11 @@
           <t>周斌持股7.70%</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>本次增资完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1486,6 +1584,11 @@
           <t>上汽科技持股3.00%</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>本次增资完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1538,6 +1641,11 @@
           <t>本次增资完成后黄山供销集团持股51.8700%</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>本次增资完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1590,6 +1698,11 @@
           <t>赛格高技术持股25.6500%</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>本次增资完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1642,6 +1755,11 @@
           <t>张俊武持股7.3150%</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>本次增资完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1694,6 +1812,11 @@
           <t>周斌持股7.3150%</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>本次增资完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1746,6 +1869,11 @@
           <t>黄山佳捷持股5%</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>本次增资完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1798,6 +1926,11 @@
           <t>上汽科技持股2.85%</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>本次增资完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1850,6 +1983,11 @@
           <t>本次整体变更后黄山供销集团持股3112.20万股</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1902,6 +2040,11 @@
           <t>赛格高技术持股1539万股</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1954,6 +2097,11 @@
           <t>张俊武持股438.90万股</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2006,6 +2154,11 @@
           <t>周斌持股438.90万股</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2058,6 +2211,11 @@
           <t>黄山佳捷持股300万股</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2108,6 +2266,11 @@
       <c r="J25" t="inlineStr">
         <is>
           <t>上汽科技持股171万股</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2299,6 +2462,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>转让类型</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2341,6 +2509,11 @@
           <t>2021年4月3日，昆山谷捷将其所持谷捷有限78%的股权以零对价转让给黄山供销集团</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>股东间转让</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2383,6 +2556,11 @@
           <t>昆山谷捷将其所持谷捷有限11%的股权以零对价转让给张俊武</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>股东间转让</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2423,6 +2601,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>昆山谷捷将其所持谷捷有限11%的股权以零对价转让给周斌</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>股东间转让</t>
         </is>
       </c>
     </row>
